--- a/StructureDefinition-access-condition.xlsx
+++ b/StructureDefinition-access-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -120,7 +120,7 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Derivation</t>

--- a/StructureDefinition-access-condition.xlsx
+++ b/StructureDefinition-access-condition.xlsx
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/StructureDefinition/access-condition</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-condition</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-access-condition.xlsx
+++ b/StructureDefinition-access-condition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="438">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -373,9 +373,6 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
@@ -467,7 +464,7 @@
     <t>assertedDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {condition-assertedDate|5.2.0}
+    <t xml:space="preserve">Extension {condition-assertedDate|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -2423,29 +2420,27 @@
       <c r="X6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Y6" s="2"/>
+      <c r="Z6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -2480,14 +2475,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2506,16 +2501,16 @@
         <v>79</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2565,7 +2560,7 @@
         <v>79</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -2589,7 +2584,7 @@
         <v>79</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>79</v>
@@ -2600,14 +2595,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2626,16 +2621,16 @@
         <v>79</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2685,7 +2680,7 @@
         <v>79</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2709,7 +2704,7 @@
         <v>79</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>79</v>
@@ -2720,10 +2715,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2746,13 +2741,13 @@
         <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2791,17 +2786,17 @@
         <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2813,7 +2808,7 @@
         <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>79</v>
@@ -2836,13 +2831,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C10" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>79</v>
@@ -2864,16 +2859,16 @@
         <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2923,7 +2918,7 @@
         <v>79</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2932,10 +2927,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>79</v>
@@ -2958,14 +2953,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2984,19 +2979,19 @@
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>79</v>
@@ -3045,7 +3040,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3057,7 +3052,7 @@
         <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>79</v>
@@ -3069,7 +3064,7 @@
         <v>79</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>79</v>
@@ -3080,10 +3075,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3106,19 +3101,19 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>79</v>
@@ -3167,7 +3162,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3182,19 +3177,19 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>79</v>
@@ -3202,10 +3197,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3228,16 +3223,16 @@
         <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3263,11 +3258,11 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3285,7 +3280,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3294,25 +3289,25 @@
         <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>79</v>
@@ -3320,10 +3315,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3346,16 +3341,16 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3381,11 +3376,11 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
@@ -3403,7 +3398,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3412,36 +3407,36 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>188</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3464,16 +3459,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3499,29 +3494,29 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y15" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3539,16 +3534,16 @@
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>79</v>
@@ -3556,13 +3551,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>79</v>
@@ -3584,16 +3579,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3619,14 +3614,14 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>204</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3643,7 +3638,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3661,16 +3656,16 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>79</v>
@@ -3678,13 +3673,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>79</v>
@@ -3706,19 +3701,19 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3743,13 +3738,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3767,7 +3762,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3785,16 +3780,16 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -3802,10 +3797,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3828,16 +3823,16 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3866,10 +3861,10 @@
         <v>115</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -3887,7 +3882,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3905,31 +3900,31 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3948,17 +3943,17 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -3983,14 +3978,14 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z19" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="Z19" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
       </c>
@@ -4007,7 +4002,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4022,30 +4017,30 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AO19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4068,13 +4063,13 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4125,7 +4120,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4149,7 +4144,7 @@
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4160,14 +4155,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4186,16 +4181,16 @@
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="N21" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4233,19 +4228,19 @@
         <v>79</v>
       </c>
       <c r="AB21" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE21" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="AC21" t="s" s="2">
+      <c r="AF21" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4257,7 +4252,7 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
@@ -4269,7 +4264,7 @@
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4280,10 +4275,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4306,19 +4301,19 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4355,17 +4350,17 @@
         <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4386,10 +4381,10 @@
         <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4400,13 +4395,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>79</v>
@@ -4428,19 +4423,19 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="N23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -4489,7 +4484,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4510,10 +4505,10 @@
         <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4524,10 +4519,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4550,13 +4545,13 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4607,7 +4602,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4631,7 +4626,7 @@
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4642,14 +4637,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4668,16 +4663,16 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="N25" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4715,19 +4710,19 @@
         <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE25" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="AC25" t="s" s="2">
+      <c r="AF25" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4739,7 +4734,7 @@
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
@@ -4751,7 +4746,7 @@
         <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -4762,10 +4757,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4791,65 +4786,65 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4870,10 +4865,10 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4884,10 +4879,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4910,16 +4905,16 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4969,7 +4964,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4990,10 +4985,10 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5004,10 +4999,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5033,14 +5028,14 @@
         <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5089,7 +5084,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5110,10 +5105,10 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5124,10 +5119,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5150,17 +5145,17 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5209,7 +5204,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5230,10 +5225,10 @@
         <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5244,10 +5239,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5270,19 +5265,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5331,7 +5326,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5352,10 +5347,10 @@
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5366,10 +5361,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5392,19 +5387,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5453,7 +5448,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5474,10 +5469,10 @@
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5488,10 +5483,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5514,16 +5509,16 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5549,14 +5544,14 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Y32" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="Y32" t="s" s="2">
+      <c r="Z32" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>321</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
       </c>
@@ -5573,7 +5568,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5591,31 +5586,31 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5634,17 +5629,17 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5693,7 +5688,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>91</v>
@@ -5708,19 +5703,19 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -5728,10 +5723,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5754,16 +5749,16 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5813,7 +5808,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5828,19 +5823,19 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>79</v>
@@ -5848,10 +5843,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5874,16 +5869,16 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5933,7 +5928,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5948,19 +5943,19 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -5968,10 +5963,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5994,16 +5989,16 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6053,7 +6048,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6062,7 +6057,7 @@
         <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>103</v>
@@ -6077,10 +6072,10 @@
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -6088,10 +6083,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6114,13 +6109,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6171,7 +6166,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6192,13 +6187,13 @@
         <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6206,10 +6201,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6232,13 +6227,13 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6289,7 +6284,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6313,10 +6308,10 @@
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -6324,10 +6319,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6350,13 +6345,13 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6407,7 +6402,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6428,13 +6423,13 @@
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6442,10 +6437,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6468,13 +6463,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6525,7 +6520,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6537,19 +6532,19 @@
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6560,10 +6555,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6586,13 +6581,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6643,7 +6638,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6667,7 +6662,7 @@
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6678,14 +6673,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6704,16 +6699,16 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="N42" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6763,7 +6758,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6775,7 +6770,7 @@
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -6787,7 +6782,7 @@
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6798,14 +6793,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6824,19 +6819,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="N43" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6885,7 +6880,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6897,7 +6892,7 @@
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
@@ -6909,7 +6904,7 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -6920,10 +6915,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6946,13 +6941,13 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6979,14 +6974,14 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7003,7 +6998,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7012,7 +7007,7 @@
         <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>103</v>
@@ -7021,13 +7016,13 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7038,10 +7033,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7064,13 +7059,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7121,7 +7116,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7130,7 +7125,7 @@
         <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>103</v>
@@ -7145,7 +7140,7 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7156,10 +7151,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7182,13 +7177,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7215,14 +7210,14 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7239,7 +7234,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7263,7 +7258,7 @@
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7274,10 +7269,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7300,16 +7295,16 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7359,7 +7354,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7371,19 +7366,19 @@
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7394,10 +7389,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7420,13 +7415,13 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7477,7 +7472,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7501,7 +7496,7 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7512,14 +7507,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7538,16 +7533,16 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7597,7 +7592,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7609,7 +7604,7 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
@@ -7621,7 +7616,7 @@
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7632,14 +7627,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7658,19 +7653,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="N50" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7719,7 +7714,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7731,7 +7726,7 @@
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
@@ -7743,7 +7738,7 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7754,10 +7749,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7780,13 +7775,13 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7813,14 +7808,14 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>423</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7837,7 +7832,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7846,25 +7841,25 @@
         <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>79</v>
@@ -7872,10 +7867,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7898,13 +7893,13 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7955,7 +7950,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7964,7 +7959,7 @@
         <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>103</v>
@@ -7979,10 +7974,10 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -7990,10 +7985,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8016,13 +8011,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8073,7 +8068,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8088,16 +8083,16 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>

--- a/StructureDefinition-access-condition.xlsx
+++ b/StructureDefinition-access-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -464,7 +464,7 @@
     <t>assertedDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {condition-assertedDate|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {condition-assertedDate|5.2.0}
 </t>
   </si>
   <si>

--- a/StructureDefinition-access-condition.xlsx
+++ b/StructureDefinition-access-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-access-condition.xlsx
+++ b/StructureDefinition-access-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
